--- a/docs/MTG要素カタログ_審査済み.xlsx
+++ b/docs/MTG要素カタログ_審査済み.xlsx
@@ -1821,12 +1821,12 @@
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M18" s="13" t="inlineStr">
         <is>
-          <t>デメリット『伝説』：自分の場に同名モンスターがいると召喚できない。-2pt 目安</t>
+          <t>【今回実装：デメリット『伝説』（`legendary`・バッチA）】（審査時は○）デメリット『伝説』：自分の場に同名モンスターがいると召喚できない。-2pt 目安</t>
         </is>
       </c>
     </row>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M22" s="13" t="inlineStr">
         <is>
-          <t>効果『装備』：モンスター1体の攻撃力+N、そのモンスターが破壊されたらこのカードを手札に戻す。攻撃力1あたり3pt</t>
+          <t>【今回実装：効果『装備』（`equip`・バッチB）】（審査時は○）効果『装備』：モンスター1体の攻撃力+N、そのモンスターが破壊されたらこのカードを手札に戻す。攻撃力1あたり3pt</t>
         </is>
       </c>
     </row>
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>条件『前の相手のターンに相手がカードを3枚以上使った』倍率0.6。コスト0化はコスト処理が要る</t>
+          <t>【今回実装：条件『前の相手のターンに相手がカードを3枚以上使った』＋能力『条件付き軽減』（コスト0化）（`enemyPlayedMany`・バッチA）】（審査時は○）条件『前の相手のターンに相手がカードを3枚以上使った』倍率0.6。コスト0化はコスト処理が要る</t>
         </is>
       </c>
     </row>
@@ -4153,12 +4153,12 @@
       </c>
       <c r="L54" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M54" s="13" t="inlineStr">
         <is>
-          <t>種族タグ（5〜8種）＋条件『同種族が2体以上』・効果『同種族1体ごとに攻撃力+N』。タグ機構が要る</t>
+          <t>【今回実装：種族タグ＋条件『同じ種族の自分のモンスターがいる』・修飾『同じ種族1体につき』・対象『同じ種族の自分のモンスター全体』（`tribe`・バッチC2）】（審査時は○）種族タグ（5〜8種）＋条件『同種族が2体以上』・効果『同種族1体ごとに攻撃力+N』。タグ機構が要る</t>
         </is>
       </c>
     </row>
@@ -4218,12 +4218,12 @@
       </c>
       <c r="L55" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M55" s="13" t="inlineStr">
         <is>
-          <t>選択式カード：効果A/Bを使用時に選ぶ。ポイントは高い方＋低い方の3割</t>
+          <t>【今回実装：モード選択（次のうち1つを選ぶ）（`modes`・バッチC2）】（審査時は○）選択式カード：効果A/Bを使用時に選ぶ。ポイントは高い方＋低い方の3割</t>
         </is>
       </c>
     </row>
@@ -4673,12 +4673,12 @@
       </c>
       <c r="L62" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M62" s="13" t="inlineStr">
         <is>
-          <t>修飾『循環』：使った後に捨て札でなく山札に混ぜる。+1pt 程度</t>
+          <t>【今回実装：カードの能力『循環』（`shuffleBack`・バッチB）】（審査時は○）修飾『循環』：使った後に捨て札でなく山札に混ぜる。+1pt 程度</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="L63" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>章付きパワー：条件『設置からNターン目』で効果が順に出て最後に消える。パワーの経過ターン管理が要る</t>
+          <t>【今回実装：英雄譚（章つきのパワー）（`saga`・バッチC2）】（審査時は○）章付きパワー：条件『設置からNターン目』で効果が順に出て最後に消える。パワーの経過ターン管理が要る</t>
         </is>
       </c>
     </row>
@@ -6290,12 +6290,12 @@
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M87" s="13" t="inlineStr">
         <is>
-          <t>キーワード『一撃離脱』：攻撃後に手札へ戻る（召喚時効果の再利用）。±0〜+6pt</t>
+          <t>【今回実装：キーワード『一撃離脱』（`hitAndRun`・バッチB）】（審査時は○）キーワード『一撃離脱』：攻撃後に手札へ戻る（召喚時効果の再利用）。±0〜+6pt</t>
         </is>
       </c>
     </row>
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L102" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M102" s="13" t="inlineStr">
         <is>
-          <t>次回：効果『討伐』（コストN以下の相手モンスターを破壊。処刑のコスト版）</t>
+          <t>【今回実装：効果『討伐』（`slay`・バッチB）】（審査時は○）次回：効果『討伐』（コストN以下の相手モンスターを破壊。処刑のコスト版）</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M109" s="13" t="inlineStr">
         <is>
-          <t>起動型能力：場のモンスター・パワーに『1エナジー：効果』ボタン（1ターン1回）。UIと行動の追加が要る</t>
+          <t>【今回実装：起動型能力（能力『起動』＋タイミング『起動』）（`activated`・バッチC1）】（審査時は○）起動型能力：場のモンスター・パワーに『1エナジー：効果』ボタン（1ターン1回）。UIと行動の追加が要る</t>
         </is>
       </c>
     </row>
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M111" s="13" t="inlineStr">
         <is>
-          <t>効果『激励』：場にいる間、自分の他のモンスターの攻撃力+N（毎回再計算）。N×3pt×体数見込み</t>
+          <t>【今回実装：キーワード『激励』（`inspire`・バッチB）】（審査時は○）効果『激励』：場にいる間、自分の他のモンスターの攻撃力+N（毎回再計算）。N×3pt×体数見込み</t>
         </is>
       </c>
     </row>
@@ -8927,12 +8927,12 @@
       </c>
       <c r="L128" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M128" s="13" t="inlineStr">
         <is>
-          <t>効果『一時奪取』：相手モンスター1体をこのターンだけ奪い速攻を与え、ターン終了時に返す。レア以上</t>
+          <t>【今回実装：効果『借用』（`borrow`・バッチB）】（審査時は○）効果『一時奪取』：相手モンスター1体をこのターンだけ奪い速攻を与え、ターン終了時に返す。レア以上</t>
         </is>
       </c>
     </row>
@@ -9695,12 +9695,12 @@
       </c>
       <c r="L140" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M140" s="13" t="inlineStr">
         <is>
-          <t>効果『蓄え』（パワー）：ターン終了時に余ったエナジーを次のターンへ持ち越す。15pt 目安</t>
+          <t>【今回実装：効果『蓄え』（`bank`・バッチB）】（審査時は○）効果『蓄え』（パワー）：ターン終了時に余ったエナジーを次のターンへ持ち越す。15pt 目安</t>
         </is>
       </c>
     </row>
@@ -10605,12 +10605,12 @@
       </c>
       <c r="L154" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M154" s="13" t="inlineStr">
         <is>
-          <t>修飾『遅延』：効果をNターン後の自分のターン開始時に発動。倍率0.7程度。遅延キューが要る</t>
+          <t>【今回実装：修飾『次のターンに（遅延）』＋遅延キュー（`nextTurn`・バッチA）】（審査時は○）修飾『遅延』：効果をNターン後の自分のターン開始時に発動。倍率0.7程度。遅延キューが要る</t>
         </is>
       </c>
     </row>
@@ -10670,12 +10670,12 @@
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M155" s="13" t="inlineStr">
         <is>
-          <t>パワーの『蓄積』：条件ごとに+1、N個で大技。パワーにカウンター枠が要る</t>
+          <t>【今回実装：蓄積カウンター（能力『蓄積』＋タイミング『蓄積がたまったとき』）（`charge`・バッチC2）】（審査時は○）パワーの『蓄積』：条件ごとに+1、N個で大技。パワーにカウンター枠が要る</t>
         </is>
       </c>
     </row>
@@ -10930,12 +10930,12 @@
       </c>
       <c r="L159" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M159" s="13" t="inlineStr">
         <is>
-          <t>条件『このモンスターが3回以上攻撃した』（探索）。モンスターごとの回数記録が要る。倍率0.6</t>
+          <t>【今回実装：条件『このモンスターが3回以上攻撃した』（`veteran`・バッチA）】（審査時は○）条件『このモンスターが3回以上攻撃した』（探索）。モンスターごとの回数記録が要る。倍率0.6</t>
         </is>
       </c>
     </row>
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L163" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M163" s="13" t="inlineStr">
         <is>
-          <t>効果『懸賞』：相手モンスター1体に印、それが倒れたら自分がN枚引く。印の管理が要る。約8pt</t>
+          <t>【今回実装：効果『懸賞』（`bounty`・バッチB）】（審査時は○）効果『懸賞』：相手モンスター1体に印、それが倒れたら自分がN枚引く。印の管理が要る。約8pt</t>
         </is>
       </c>
     </row>
@@ -11710,12 +11710,12 @@
       </c>
       <c r="L171" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M171" s="13" t="inlineStr">
         <is>
-          <t>次回：効果『準備』（次のターンに引く枚数+N）に統合（#420）</t>
+          <t>【今回実装：効果『準備』（`prepare`・バッチB）】（審査時は○）次回：効果『準備』（次のターンに引く枚数+N）に統合（#420）</t>
         </is>
       </c>
     </row>
@@ -12551,12 +12551,12 @@
       </c>
       <c r="L184" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M184" s="13" t="inlineStr">
         <is>
-          <t>『王冠』：保持中はターン終了時に1枚ドロー。プレイヤーにダメージを通されると奪われる。攻める理由になる</t>
+          <t>【今回実装：王冠（効果『王冠を得る』・条件『王冠を持っている』）（`monarch`・バッチC2）】（審査時は○）『王冠』：保持中はターン終了時に1枚ドロー。プレイヤーにダメージを通されると奪われる。攻める理由になる</t>
         </is>
       </c>
     </row>
@@ -12811,12 +12811,12 @@
       </c>
       <c r="L188" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M188" s="13" t="inlineStr">
         <is>
-          <t>#387 の速度ゲージに統合（次回）</t>
+          <t>【今回実装：速度ゲージ（効果『エンジン始動』・条件『速度が最大』）（`speedGauge`・バッチC2）】（審査時は○）#387 の速度ゲージに統合（次回）</t>
         </is>
       </c>
     </row>
@@ -14826,12 +14826,12 @@
       </c>
       <c r="L219" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M219" s="13" t="inlineStr">
         <is>
-          <t>次回：キーワード『護法』（対象にするとコスト+1）。対象で変わるコストはドラッグ操作の改修後に</t>
+          <t>【今回実装：キーワード『護法』（`ward`・バッチB）】（審査時は○）次回：キーワード『護法』（対象にするとコスト+1）。対象で変わるコストはドラッグ操作の改修後に</t>
         </is>
       </c>
     </row>
@@ -15281,12 +15281,12 @@
       </c>
       <c r="L226" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M226" s="13" t="inlineStr">
         <is>
-          <t>キーワード『再利用』：使用後に手札へ戻る（1ターン1回）。エナジーで制限。基礎pt×0.8上乗せ</t>
+          <t>【今回実装：カードの能力『再利用』（`buyback`・バッチB）】（審査時は○）キーワード『再利用』：使用後に手札へ戻る（1ターン1回）。エナジーで制限。基礎pt×0.8上乗せ</t>
         </is>
       </c>
     </row>
@@ -15411,12 +15411,12 @@
       </c>
       <c r="L228" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M228" s="13" t="inlineStr">
         <is>
-          <t>カードの属性『サイクリング』：手札からエナジー1で捨てて1枚引く。新しい行動（ドロップ先）が要る。+2pt</t>
+          <t>【今回実装：カードの能力『サイクリング』（行動 handAbility）（`cycling`・バッチC1）】（審査時は○）カードの属性『サイクリング』：手札からエナジー1で捨てて1枚引く。新しい行動（ドロップ先）が要る。+2pt</t>
         </is>
       </c>
     </row>
@@ -15736,12 +15736,12 @@
       </c>
       <c r="L233" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M233" s="13" t="inlineStr">
         <is>
-          <t>条件『キッカー』：エナジーを追加で1払えるなら払って発動。使用時の自動支払いで実装。倍率0.8</t>
+          <t>【今回実装：カードの能力『キッカー』＋条件『キッカーを払っていれば』（`kicker`・バッチC1）】（審査時は○）条件『キッカー』：エナジーを追加で1払えるなら払って発動。使用時の自動支払いで実装。倍率0.8</t>
         </is>
       </c>
     </row>
@@ -15866,12 +15866,12 @@
       </c>
       <c r="L235" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M235" s="13" t="inlineStr">
         <is>
-          <t>キーワード『フラッシュバック』：捨て札から使え、使ったら除外。捨て札から使う操作が要る。基礎pt×0.6上乗せ</t>
+          <t>【今回実装：カードの能力『フラッシュバック』（捨て札から使う）（`flashback`・バッチC1）】（審査時は○）キーワード『フラッシュバック』：捨て札から使え、使ったら除外。捨て札から使う操作が要る。基礎pt×0.6上乗せ</t>
         </is>
       </c>
     </row>
@@ -16386,12 +16386,12 @@
       </c>
       <c r="L243" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M243" s="13" t="inlineStr">
         <is>
-          <t>キーワード『親和』：自分の場のモンスター1体につきコスト−1（最低0か1）。動的コストの仕組みが要る</t>
+          <t>【今回実装：カードの能力『親和』（`affinity`・バッチC1）】（審査時は○）キーワード『親和』：自分の場のモンスター1体につきコスト−1（最低0か1）。動的コストの仕組みが要る</t>
         </is>
       </c>
     </row>
@@ -16451,12 +16451,12 @@
       </c>
       <c r="L244" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M244" s="13" t="inlineStr">
         <is>
-          <t>#54・#599 の選択式カードに統合（次回）</t>
+          <t>【今回実装：カードの能力『双呪』（モード選択）（`entwine`・バッチC2）】（審査時は○）#54・#599 の選択式カードに統合（次回）</t>
         </is>
       </c>
     </row>
@@ -18206,12 +18206,12 @@
       </c>
       <c r="L271" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M271" s="13" t="inlineStr">
         <is>
-          <t>キーワード『猛襲N』：相手プレイヤーを攻撃するとき攻撃力+N。+N×2pt</t>
+          <t>【今回実装：キーワード『猛襲』（`onslaught`・バッチB）】（審査時は○）キーワード『猛襲N』：相手プレイヤーを攻撃するとき攻撃力+N。+N×2pt</t>
         </is>
       </c>
     </row>
@@ -19311,12 +19311,12 @@
       </c>
       <c r="L288" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M288" s="13" t="inlineStr">
         <is>
-          <t>効果『続唱』：山札からこのカードより軽いカードが出るまでめくり無料で使う。対象自動選択が要る</t>
+          <t>【今回実装：効果『続唱』（無料で使う）（`cascade`・バッチB）】（審査時は○）効果『続唱』：山札からこのカードより軽いカードが出るまでめくり無料で使う。対象自動選択が要る</t>
         </is>
       </c>
     </row>
@@ -19506,12 +19506,12 @@
       </c>
       <c r="L291" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M291" s="13" t="inlineStr">
         <is>
-          <t>キーワード『反復』：使用後、次の自分のターン開始時に同じ効果がもう一度発動。基礎pt×0.7上乗せ</t>
+          <t>【今回実装：カードの能力『反復』（`rebound`・バッチB）】（審査時は○）キーワード『反復』：使用後、次の自分のターン開始時に同じ効果がもう一度発動。基礎pt×0.7上乗せ</t>
         </is>
       </c>
     </row>
@@ -19701,12 +19701,12 @@
       </c>
       <c r="L294" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M294" s="13" t="inlineStr">
         <is>
-          <t>キーワード『鼓舞N』：攻撃するたび他の自分のモンスターの攻撃力+N（このターン）。+N×2pt</t>
+          <t>【今回実装：対象『自分の他のモンスター全体』（攻撃するたび＋一時強化＋この対象＝喊声）（`otherAllies`・バッチA）】（審査時は○）キーワード『鼓舞N』：攻撃するたび他の自分のモンスターの攻撃力+N（このターン）。+N×2pt</t>
         </is>
       </c>
     </row>
@@ -19896,12 +19896,12 @@
       </c>
       <c r="L297" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M297" s="13" t="inlineStr">
         <is>
-          <t>タイミング『引いたとき』（ターン開始のドロー含む）。寄生の仕組みを流用</t>
+          <t>【今回実装：タイミング『引いたとき』（`drawn`・バッチA）】（審査時は○）タイミング『引いたとき』（ターン開始のドロー含む）。寄生の仕組みを流用</t>
         </is>
       </c>
     </row>
@@ -21001,12 +21001,12 @@
       </c>
       <c r="L314" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M314" s="13" t="inlineStr">
         <is>
-          <t>条件『生け贄』：使用時に自分のモンスター1体を破壊してよく、したら追加効果。選択UI要。倍率0.6</t>
+          <t>【今回実装：条件『自分のモンスター1体を生け贄にしたなら』（濫用）（`exploit`・バッチA）】（審査時は○）条件『生け贄』：使用時に自分のモンスター1体を破壊してよく、したら追加効果。選択UI要。倍率0.6</t>
         </is>
       </c>
     </row>
@@ -21066,12 +21066,12 @@
       </c>
       <c r="L315" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M315" s="13" t="inlineStr">
         <is>
-          <t>次回：キーワード『威圧』（攻撃時に反撃を受けない）。今回は先制攻撃で一部代替</t>
+          <t>【今回実装：キーワード『威圧』（`menace`・バッチB）】（審査時は○）次回：キーワード『威圧』（攻撃時に反撃を受けない）。今回は先制攻撃で一部代替</t>
         </is>
       </c>
     </row>
@@ -21326,12 +21326,12 @@
       </c>
       <c r="L319" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M319" s="13" t="inlineStr">
         <is>
-          <t>次回：タイミング hitEnemyPlayer＋効果『切削』で表現。循環式なので効きは弱い</t>
+          <t>【今回実装：効果『切削』（相手）＋既存のタイミング『相手プレイヤーにダメージを与えたとき』（`mill`・バッチB）】（審査時は○）次回：タイミング hitEnemyPlayer＋効果『切削』で表現。循環式なので効きは弱い</t>
         </is>
       </c>
     </row>
@@ -21456,12 +21456,12 @@
       </c>
       <c r="L321" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M321" s="13" t="inlineStr">
         <is>
-          <t>カードの『条件付きコスト軽減』：このターン2枚目以降ならコスト−1（条件は既存のnthCard系を流用）。+8pt</t>
+          <t>【今回実装：カードの能力『条件付き軽減』＋条件『このターン2枚目以降に使う』（怒濤）（`costCut`・バッチC1）】（審査時は○）カードの『条件付きコスト軽減』：このターン2枚目以降ならコスト−1（条件は既存のnthCard系を流用）。+8pt</t>
         </is>
       </c>
     </row>
@@ -21846,12 +21846,12 @@
       </c>
       <c r="L327" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M327" s="13" t="inlineStr">
         <is>
-          <t>効果『トークン生成』とセット：召喚時に「攻撃力/体力+N」か「1/1の小鬼N体」を選ぶ。選択UI要</t>
+          <t>【今回実装：モード選択（鍛錬／トークン生成を選ぶ＝製造）（`modes`・バッチC2）】（審査時は○）効果『トークン生成』とセット：召喚時に「攻撃力/体力+N」か「1/1の小鬼N体」を選ぶ。選択UI要</t>
         </is>
       </c>
     </row>
@@ -22431,12 +22431,12 @@
       </c>
       <c r="L336" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M336" s="13" t="inlineStr">
         <is>
-          <t>捨て札から使える後半効果（『余韻』）：捨て札にある間に1回だけ使え、使ったら除外。捨て札使用の仕組み要</t>
+          <t>【今回実装：タイミング『捨て札から使ったとき』＋捨て札から使う能力（余波）（`fromDiscard`・バッチC1）】（審査時は○）捨て札から使える後半効果（『余韻』）：捨て札にある間に1回だけ使え、使ったら除外。捨て札使用の仕組み要</t>
         </is>
       </c>
     </row>
@@ -22821,12 +22821,12 @@
       </c>
       <c r="L342" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M342" s="13" t="inlineStr">
         <is>
-          <t>キーワード（カード）『再活』：捨て札から、手札1枚を捨てて使える。使ったら除外。捨て札から使う仕組み要。+15pt</t>
+          <t>【今回実装：カードの能力『再活』（捨て札から使う）（`jumpStart`・バッチC1）】（審査時は○）キーワード（カード）『再活』：捨て札から、手札1枚を捨てて使える。使ったら除外。捨て札から使う仕組み要。+15pt</t>
         </is>
       </c>
     </row>
@@ -23016,12 +23016,12 @@
       </c>
       <c r="L345" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M345" s="13" t="inlineStr">
         <is>
-          <t>キーワード『暴動』：召喚時に速攻か攻撃力+N/体力+Nを選ぶ。選択UI＋CPU選び。速攻ptの7割</t>
+          <t>【今回実装：モード選択（速攻の付与／鍛錬を選ぶ＝暴動）（`modes`・バッチC2）】（審査時は○）キーワード『暴動』：召喚時に速攻か攻撃力+N/体力+Nを選ぶ。選択UI＋CPU選び。速攻ptの7割</t>
         </is>
       </c>
     </row>
@@ -23146,12 +23146,12 @@
       </c>
       <c r="L347" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M347" s="13" t="inlineStr">
         <is>
-          <t>『脱出』：捨て札からも使え、他の捨て札N枚を除外する。捨て札使用の仕組み要。再活とまとめる</t>
+          <t>【今回実装：カードの能力『脱出』（捨て札から使う）（`escape`・バッチC1）】（審査時は○）『脱出』：捨て札からも使え、他の捨て札N枚を除外する。捨て札使用の仕組み要。再活とまとめる</t>
         </is>
       </c>
     </row>
@@ -23861,12 +23861,12 @@
       </c>
       <c r="L358" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M358" s="13" t="inlineStr">
         <is>
-          <t>キーワード『訓練N』：攻撃力がこれより高い味方がいる状態で攻撃するたび攻撃力+N/体力+N。進化と重複気味</t>
+          <t>【今回実装：条件『このモンスターより攻撃力の高い自分のモンスターがいる』（攻撃するたび＋鍛錬＝訓練）（`strongerAlly`・バッチA）】（審査時は○）キーワード『訓練N』：攻撃力がこれより高い味方がいる状態で攻撃するたび攻撃力+N/体力+N。進化と重複気味</t>
         </is>
       </c>
     </row>
@@ -25551,12 +25551,12 @@
       </c>
       <c r="L384" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M384" s="13" t="inlineStr">
         <is>
-          <t>召喚時に『トークン生成』で1/1のコピー。トークン実装後、能力の複製は重いので数値のみ</t>
+          <t>【今回実装：効果『新生』（複写トークン。キッカーと組める）（`offspring`・バッチB）】（審査時は○）召喚時に『トークン生成』で1/1のコピー。トークン実装後、能力の複製は重いので数値のみ</t>
         </is>
       </c>
     </row>
@@ -25746,12 +25746,12 @@
       </c>
       <c r="L387" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M387" s="13" t="inlineStr">
         <is>
-          <t>条件『速度が最大』。速度ゲージ（387）とセット</t>
+          <t>【今回実装：速度ゲージの条件『速度が最大』（`maxSpeed`・バッチC2）】（審査時は○）条件『速度が最大』。速度ゲージ（387）とセット</t>
         </is>
       </c>
     </row>
@@ -25811,12 +25811,12 @@
       </c>
       <c r="L388" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M388" s="13" t="inlineStr">
         <is>
-          <t>プレイヤーの『速度』ゲージ：自ターンに相手にダメージを与えると1上がる（最大4）。新しい資源要</t>
+          <t>【今回実装：速度ゲージの効果『エンジン始動』（`startEngine`・バッチC2）】（審査時は○）プレイヤーの『速度』ゲージ：自ターンに相手にダメージを与えると1上がる（最大4）。新しい資源要</t>
         </is>
       </c>
     </row>
@@ -25941,12 +25941,12 @@
       </c>
       <c r="L390" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M390" s="13" t="inlineStr">
         <is>
-          <t>攻撃するたび『トークン生成』（1/1をN体、ターン終了時に消える）。一時トークン</t>
+          <t>【今回実装：トークン生成の選択肢『応召』（攻撃するたび＋応召のトークン）（`tokenMobilize`・バッチB）】（審査時は○）攻撃するたび『トークン生成』（1/1をN体、ターン終了時に消える）。一時トークン</t>
         </is>
       </c>
     </row>
@@ -26786,12 +26786,12 @@
       </c>
       <c r="L403" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M403" s="13" t="inlineStr">
         <is>
-          <t>条件『自分のモンスターの攻撃力合計がN以上』。倍率0.7</t>
+          <t>【今回実装：条件『自分のモンスターの攻撃力の合計が8以上』（`totalAttack`・バッチA）】（審査時は○）条件『自分のモンスターの攻撃力合計がN以上』。倍率0.7</t>
         </is>
       </c>
     </row>
@@ -27038,12 +27038,12 @@
       </c>
       <c r="L407" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M407" s="13" t="inlineStr">
         <is>
-          <t>起動型能力：場のモンスター/パワーに『エナジー1：効果』（ターン1回）。UIとCPUに選択追加が要る</t>
+          <t>【今回実装：起動型能力（行動 activate）（`activated`・バッチC1）】（審査時は○）起動型能力：場のモンスター/パワーに『エナジー1：効果』（ターン1回）。UIとCPUに選択追加が要る</t>
         </is>
       </c>
     </row>
@@ -27298,12 +27298,12 @@
       </c>
       <c r="L411" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M411" s="13" t="inlineStr">
         <is>
-          <t>効果『封殺』：相手が次に使うカード1枚を無効化（予約型）。割り込み不要。高め約30pt、レア以上</t>
+          <t>【今回実装：効果『封殺』（予約型の打ち消し）（`quash`・バッチB）】（審査時は○）効果『封殺』：相手が次に使うカード1枚を無効化（予約型）。割り込み不要。高め約30pt、レア以上</t>
         </is>
       </c>
     </row>
@@ -27948,12 +27948,12 @@
       </c>
       <c r="L421" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M421" s="13" t="inlineStr">
         <is>
-          <t>次回：効果『準備』（次のターンに引く枚数+N。1枚約3pt）</t>
+          <t>【今回実装：効果『準備』（`prepare`・バッチB）】（審査時は○）次回：効果『準備』（次のターンに引く枚数+N。1枚約3pt）</t>
         </is>
       </c>
     </row>
@@ -28013,12 +28013,12 @@
       </c>
       <c r="L422" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M422" s="13" t="inlineStr">
         <is>
-          <t>次回：効果『切削』（自分の山札の上N枚を捨て札へ。捨て札条件の燃料）</t>
+          <t>【今回実装：効果『切削』（`mill`・バッチB）】（審査時は○）次回：効果『切削』（自分の山札の上N枚を捨て札へ。捨て札条件の燃料）</t>
         </is>
       </c>
     </row>
@@ -28923,12 +28923,12 @@
       </c>
       <c r="L436" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M436" s="13" t="inlineStr">
         <is>
-          <t>次回検討：山札のコスト次第で確率が偏る。運の条件は今回コイン投げで足りる</t>
+          <t>【今回実装：条件『激突に勝つ』（`clash`・バッチA）】（審査時は○）次回検討：山札のコスト次第で確率が偏る。運の条件は今回コイン投げで足りる</t>
         </is>
       </c>
     </row>
@@ -29183,12 +29183,12 @@
       </c>
       <c r="L440" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M440" s="13" t="inlineStr">
         <is>
-          <t>次回：効果『増殖』。今回の『倍化』と役割が近いので後回し</t>
+          <t>【今回実装：効果『増殖』（`proliferate`・バッチB）】（審査時は○）次回：効果『増殖』。今回の『倍化』と役割が近いので後回し</t>
         </is>
       </c>
     </row>
@@ -29313,12 +29313,12 @@
       </c>
       <c r="L442" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M442" s="13" t="inlineStr">
         <is>
-          <t>効果『居住』：自分のトークン1体を複製。トークン生成が前提</t>
+          <t>【今回実装：効果『居住』（`populate`・バッチB）】（審査時は○）効果『居住』：自分のトークン1体を複製。トークン生成が前提</t>
         </is>
       </c>
     </row>
@@ -29508,12 +29508,12 @@
       </c>
       <c r="L445" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M445" s="13" t="inlineStr">
         <is>
-          <t>次回：対象『いちばん体力の低い自分のモンスター』</t>
+          <t>【今回実装：対象『いちばん体力の低い自分のモンスター』（鍛錬＋この対象＝鼓舞）（`weakestAlly`・バッチA）】（審査時は○）次回：対象『いちばん体力の低い自分のモンスター』</t>
         </is>
       </c>
     </row>
@@ -29703,12 +29703,12 @@
       </c>
       <c r="L448" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M448" s="13" t="inlineStr">
         <is>
-          <t>次回：デメリット『消耗』。今回の『腐乱』と近い</t>
+          <t>【今回実装：デメリット『消耗』（`exert`・バッチA）】（審査時は○）次回：デメリット『消耗』。今回の『腐乱』と近い</t>
         </is>
       </c>
     </row>
@@ -29768,12 +29768,12 @@
       </c>
       <c r="L449" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M449" s="13" t="inlineStr">
         <is>
-          <t>効果『探検』：山札の一番上を公開、モンスターなら手札へ、違えば自分のモンスター1体を鍛錬+N</t>
+          <t>【今回実装：効果『探検』（`explore`・バッチB）】（審査時は○）効果『探検』：山札の一番上を公開、モンスターなら手札へ、違えば自分のモンスター1体を鍛錬+N</t>
         </is>
       </c>
     </row>
@@ -29963,12 +29963,12 @@
       </c>
       <c r="L452" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M452" s="13" t="inlineStr">
         <is>
-          <t>効果『動員』：『軍団』トークンが無ければ出し、攻撃力/体力+N。トークン前提</t>
+          <t>【今回実装：効果『動員』（軍団トークン）（`amass`・バッチB）】（審査時は○）効果『動員』：『軍団』トークンが無ければ出し、攻撃力/体力+N。トークン前提</t>
         </is>
       </c>
     </row>
@@ -30613,12 +30613,12 @@
       </c>
       <c r="L462" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M462" s="13" t="inlineStr">
         <is>
-          <t>効果『発見』：山札からコストN以下を1枚ランダムに無料で使う。対象選択の流れが要る</t>
+          <t>【今回実装：効果『続唱』（コストN以下を無料で使う。発見を統合）（`cascade`・バッチB）】（審査時は○）効果『発見』：山札からコストN以下を1枚ランダムに無料で使う。対象選択の流れが要る</t>
         </is>
       </c>
     </row>
@@ -30743,12 +30743,12 @@
       </c>
       <c r="L464" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M464" s="13" t="inlineStr">
         <is>
-          <t>追加コスト『証拠収集』：捨て札からコスト合計N以上を除外して追加効果。条件の一種</t>
+          <t>【今回実装：デメリット『捨て札の除外』（コスト合計＝証拠収集）（`exileDiscard`・バッチA）】（審査時は○）追加コスト『証拠収集』：捨て札からコスト合計N以上を除外して追加効果。条件の一種</t>
         </is>
       </c>
     </row>
@@ -30873,12 +30873,12 @@
       </c>
       <c r="L466" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M466" s="13" t="inlineStr">
         <is>
-          <t>追加コスト『捨て札3枚を除外』（給餌）。#463と同じ枠</t>
+          <t>【今回実装：デメリット『捨て札の除外』（枚数＝給餌）（`exileDiscard`・バッチA）】（審査時は○）追加コスト『捨て札3枚を除外』（給餌）。#463と同じ枠</t>
         </is>
       </c>
     </row>
@@ -31263,12 +31263,12 @@
       </c>
       <c r="L472" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M472" s="13" t="inlineStr">
         <is>
-          <t>効果『動力化』：自分のモンスター1体をこのターン攻撃不可にしてエナジー+1</t>
+          <t>【今回実装：効果『動力化』（`harness`・バッチB）】（審査時は○）効果『動力化』：自分のモンスター1体をこのターン攻撃不可にしてエナジー+1</t>
         </is>
       </c>
     </row>
@@ -31328,12 +31328,12 @@
       </c>
       <c r="L473" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M473" s="13" t="inlineStr">
         <is>
-          <t>次回：デメリット『枯朽』（衰弱の自分向け版）</t>
+          <t>【今回実装：デメリット『枯朽』（`blight`・バッチA）】（審査時は○）次回：デメリット『枯朽』（衰弱の自分向け版）</t>
         </is>
       </c>
     </row>
@@ -31458,12 +31458,12 @@
       </c>
       <c r="L475" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M475" s="13" t="inlineStr">
         <is>
-          <t>効果『徴募』：謀議＋捨てたのがスキルなら1/1トークン。トークン前提</t>
+          <t>【今回実装：効果『徴募』（`recruit`・バッチB）】（審査時は○）効果『徴募』：謀議＋捨てたのがスキルなら1/1トークン。トークン前提</t>
         </is>
       </c>
     </row>
@@ -31771,12 +31771,12 @@
       </c>
       <c r="L480" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M480" s="13" t="inlineStr">
         <is>
-          <t>#183『王冠』と同じ</t>
+          <t>【今回実装：王冠（#183 と同じ）（`monarch`・バッチC2）】（審査時は○）#183『王冠』と同じ</t>
         </is>
       </c>
     </row>
@@ -32096,12 +32096,12 @@
       </c>
       <c r="L485" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M485" s="13" t="inlineStr">
         <is>
-          <t>条件『このターン自分のモンスターが2回以上攻撃した』倍率0.6（#522の上位）</t>
+          <t>【今回実装：条件『このターン自分のモンスターが2回以上攻撃した』（`twoAllyAttacks`・バッチA）】（審査時は○）条件『このターン自分のモンスターが2回以上攻撃した』倍率0.6（#522の上位）</t>
         </is>
       </c>
     </row>
@@ -32291,12 +32291,12 @@
       </c>
       <c r="L488" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M488" s="13" t="inlineStr">
         <is>
-          <t>2WAY『魂力』：手札から捨てて別効果を使う行動を追加。高い方の価値で価格</t>
+          <t>【今回実装：カードの能力『魂力』（行動 handAbility）（`channel`・バッチC1）】（審査時は○）2WAY『魂力』：手札から捨てて別効果を使う行動を追加。高い方の価値で価格</t>
         </is>
       </c>
     </row>
@@ -32681,12 +32681,12 @@
       </c>
       <c r="L494" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M494" s="13" t="inlineStr">
         <is>
-          <t>条件『攻撃力がすべて違う自分のモンスターが3体以上』倍率0.5</t>
+          <t>【今回実装：条件『攻撃力の違う自分のモンスターが3体以上』（`coven`・バッチA）】（審査時は○）条件『攻撃力がすべて違う自分のモンスターが3体以上』倍率0.5</t>
         </is>
       </c>
     </row>
@@ -32746,12 +32746,12 @@
       </c>
       <c r="L495" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M495" s="13" t="inlineStr">
         <is>
-          <t>条件『捨て札にカードの種類が3種類以上』倍率0.7（呪いを含む4種なら0.5）</t>
+          <t>【今回実装：条件『捨て札にカードの種類が3種類以上』（`delirium`・バッチA）】（審査時は○）条件『捨て札にカードの種類が3種類以上』倍率0.7（呪いを含む4種なら0.5）</t>
         </is>
       </c>
     </row>
@@ -33201,12 +33201,12 @@
       </c>
       <c r="L502" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M502" s="13" t="inlineStr">
         <is>
-          <t>次回：条件『HPが1/4以下』。既存『HPが半分以下』の厳しい版</t>
+          <t>【今回実装：条件『自分のHPが4分の1以下』（`criticalHp`・バッチA）】（審査時は○）次回：条件『HPが1/4以下』。既存『HPが半分以下』の厳しい版</t>
         </is>
       </c>
     </row>
@@ -33461,12 +33461,12 @@
       </c>
       <c r="L506" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M506" s="13" t="inlineStr">
         <is>
-          <t>条件『自分のモンスターの攻撃力合計8（基）以上』倍率0.6（#503と近い）</t>
+          <t>【今回実装：条件『自分のモンスターの攻撃力の合計が8以上』（#402 と統合）（`totalAttack`・バッチA）】（審査時は○）条件『自分のモンスターの攻撃力合計8（基）以上』倍率0.6（#503と近い）</t>
         </is>
       </c>
     </row>
@@ -33656,12 +33656,12 @@
       </c>
       <c r="L509" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M509" s="13" t="inlineStr">
         <is>
-          <t>次回：タイミング『このモンスターが自分のカードの対象になるたび』</t>
+          <t>【今回実装：タイミング『自分のカードの対象になるたび』（`targeted`・バッチA）】（審査時は○）次回：タイミング『このモンスターが自分のカードの対象になるたび』</t>
         </is>
       </c>
     </row>
@@ -34306,12 +34306,12 @@
       </c>
       <c r="L519" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M519" s="13" t="inlineStr">
         <is>
-          <t>条件『このターン相手に合計N（基6）以上ダメージを与えた』倍率0.6</t>
+          <t>【今回実装：条件『このターン相手に合計6以上のダメージを与えた』（`bigDamageThisTurn`・バッチA）】（審査時は○）条件『このターン相手に合計N（基6）以上ダメージを与えた』倍率0.6</t>
         </is>
       </c>
     </row>
@@ -34891,12 +34891,12 @@
       </c>
       <c r="L528" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M528" s="13" t="inlineStr">
         <is>
-          <t>条件『捨て札にスキルが2枚以上』倍率0.85（満たしやすい）</t>
+          <t>【今回実装：条件『捨て札にスキルが2枚以上』（`skillsInDiscard`・バッチA）】（審査時は○）条件『捨て札にスキルが2枚以上』倍率0.85（満たしやすい）</t>
         </is>
       </c>
     </row>
@@ -35281,12 +35281,12 @@
       </c>
       <c r="L534" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M534" s="13" t="inlineStr">
         <is>
-          <t>修飾『捨て札のモンスター1枚につき効果量+N（上限5枚）』。比例の仕組みが要る</t>
+          <t>【今回実装：修飾『捨て札のモンスター1枚につき』（`perDiscardMonster`・バッチA）】（審査時は○）修飾『捨て札のモンスター1枚につき効果量+N（上限5枚）』。比例の仕組みが要る</t>
         </is>
       </c>
     </row>
@@ -35671,12 +35671,12 @@
       </c>
       <c r="L540" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M540" s="13" t="inlineStr">
         <is>
-          <t>次回：条件『このターン自分が回復した』</t>
+          <t>【今回実装：条件『このターン自分が回復した』（`healedThisTurn`・バッチA）】（審査時は○）次回：条件『このターン自分が回復した』</t>
         </is>
       </c>
     </row>
@@ -35736,12 +35736,12 @@
       </c>
       <c r="L541" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M541" s="13" t="inlineStr">
         <is>
-          <t>タイミング『コスト3以上のカードを使うたび』。カードを使うたびの絞り込み版</t>
+          <t>【今回実装：タイミング『コスト3以上のカードを使うたび』（`bigCardPlayed`・バッチA）】（審査時は○）タイミング『コスト3以上のカードを使うたび』。カードを使うたびの絞り込み版</t>
         </is>
       </c>
     </row>
@@ -35923,12 +35923,12 @@
       </c>
       <c r="L544" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M544" s="13" t="inlineStr">
         <is>
-          <t>条件『相手の毒が3（基）以上』倍率0.7。既存『相手が毒状態』の閾値版</t>
+          <t>【今回実装：条件『相手の毒が3以上』（`enemyPoisonHigh`・バッチA）】（審査時は○）条件『相手の毒が3（基）以上』倍率0.7。既存『相手が毒状態』の閾値版</t>
         </is>
       </c>
     </row>
@@ -36228,12 +36228,12 @@
       </c>
       <c r="L549" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M549" s="13" t="inlineStr">
         <is>
-          <t>効果『同士討ち』：相手モンスター全員が攻撃力ぶん互いにランダムな相手を殴る。20pt目安</t>
+          <t>【今回実装：効果『同士討ち』（`infight`・バッチB）】（審査時は○）効果『同士討ち』：相手モンスター全員が攻撃力ぶん互いにランダムな相手を殴る。20pt目安</t>
         </is>
       </c>
     </row>
@@ -36350,12 +36350,12 @@
       </c>
       <c r="L551" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M551" s="13" t="inlineStr">
         <is>
-          <t>次回：効果『抽出』（山札から指定種類をランダムに1枚。サーチの廉価版）</t>
+          <t>【今回実装：効果『抽出』（`seek`・バッチB）】（審査時は○）次回：効果『抽出』（山札から指定種類をランダムに1枚。サーチの廉価版）</t>
         </is>
       </c>
     </row>
@@ -36411,12 +36411,12 @@
       </c>
       <c r="L552" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M552" s="13" t="inlineStr">
         <is>
-          <t>効果『創出』：手札に使い切りのトークンカード（例：コスト0・ダメージN、使うと除外）を加える。中身ぶん+5pt</t>
+          <t>【今回実装：効果『創出』（`conjure`・バッチB）】（審査時は○）効果『創出』：手札に使い切りのトークンカード（例：コスト0・ダメージN、使うと除外）を加える。中身ぶん+5pt</t>
         </is>
       </c>
     </row>
@@ -36533,12 +36533,12 @@
       </c>
       <c r="L554" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M554" s="13" t="inlineStr">
         <is>
-          <t>効果『発見』：山札の上3枚から1枚を選んで手札へ、残りは捨て札。選択UIはサーチと共用。約12pt</t>
+          <t>【今回実装：効果『発見』（上3枚から1枚を選ぶ）（`discover`・バッチB）】（審査時は○）効果『発見』：山札の上3枚から1枚を選んで手札へ、残りは捨て札。選択UIはサーチと共用。約12pt</t>
         </is>
       </c>
     </row>
@@ -36594,12 +36594,12 @@
       </c>
       <c r="L555" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M555" s="13" t="inlineStr">
         <is>
-          <t>効果『成長』：使うたびこのカードのダメージ+N（対戦中ずっと、カード個体に保存）。個体カウンターが要る。+8pt目安</t>
+          <t>【今回実装：カードの能力『成長』（`grow`・バッチB）】（審査時は○）効果『成長』：使うたびこのカードのダメージ+N（対戦中ずっと、カード個体に保存）。個体カウンターが要る。+8pt目安</t>
         </is>
       </c>
     </row>
@@ -36777,12 +36777,12 @@
       </c>
       <c r="L558" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M558" s="13" t="inlineStr">
         <is>
-          <t>状態『恩恵』：次のアタックM回、ダメージ+N（回数制）。筋力と気合の中間。回数×N×2pt程度</t>
+          <t>【今回実装：効果『恩恵』（`boon`・バッチB）】（審査時は○）状態『恩恵』：次のアタックM回、ダメージ+N（回数制）。筋力と気合の中間。回数×N×2pt程度</t>
         </is>
       </c>
     </row>
@@ -36838,12 +36838,12 @@
       </c>
       <c r="L559" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M559" s="13" t="inlineStr">
         <is>
-          <t>キーワード『分身』：初めて攻撃したとき、分身を失った自分のコピーを手札に加える。複製の仕組みを流用。+本体の4割</t>
+          <t>【今回実装：キーワード『分身』（`doubleTeam`・バッチB）】（審査時は○）キーワード『分身』：初めて攻撃したとき、分身を失った自分のコピーを手札に加える。複製の仕組みを流用。+本体の4割</t>
         </is>
       </c>
     </row>
@@ -39311,12 +39311,12 @@
       </c>
       <c r="L600" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M600" s="13" t="inlineStr">
         <is>
-          <t>『次のうち1つを選ぶ』：効果ごとに選択肢グループを持たせる。最大モードの価格+20%。選択UIが要る</t>
+          <t>【今回実装：モード選択（次のうち1つを選ぶ）（`modes`・バッチC2）】（審査時は○）『次のうち1つを選ぶ』：効果ごとに選択肢グループを持たせる。最大モードの価格+20%。選択UIが要る</t>
         </is>
       </c>
     </row>
@@ -39441,12 +39441,12 @@
       </c>
       <c r="L602" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M602" s="13" t="inlineStr">
         <is>
-          <t>効果『封じ』：相手が次に使うカード1枚の効果を無効にする（罠状態）。割り込み不要。約30pt</t>
+          <t>【今回実装：効果『封殺』（#410 と統合）（`quash`・バッチB）】（審査時は○）効果『封じ』：相手が次に使うカード1枚の効果を無効にする（罠状態）。割り込み不要。約30pt</t>
         </is>
       </c>
     </row>
@@ -39872,12 +39872,12 @@
       </c>
       <c r="L609" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M609" s="13" t="inlineStr">
         <is>
-          <t>カード属性『親和』：このターン使ったカード1枚ごとにコスト−1。手札のコストを動的計算する仕組みが要る</t>
+          <t>【今回実装：カードの能力『親和』（このターン使ったカード1枚につき）（`affinity`・バッチC1）】（審査時は○）カード属性『親和』：このターン使ったカード1枚ごとにコスト−1。手札のコストを動的計算する仕組みが要る</t>
         </is>
       </c>
     </row>
@@ -40124,12 +40124,12 @@
       </c>
       <c r="L613" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M613" s="13" t="inlineStr">
         <is>
-          <t>カードに種族タグを付け、条件『同じ種族が自分の場にいる』で参照。タグ欄の追加が要る。倍率0.7</t>
+          <t>【今回実装：種族タグ（#53 と統合）（`tribe`・バッチC2）】（審査時は○）カードに種族タグを付け、条件『同じ種族が自分の場にいる』で参照。タグ欄の追加が要る。倍率0.7</t>
         </is>
       </c>
     </row>
@@ -40185,12 +40185,12 @@
       </c>
       <c r="L614" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M614" s="13" t="inlineStr">
         <is>
-          <t>対象『お互い』：ドロー・回復などを両者に。相手にも利益があるので価格×0.4</t>
+          <t>【今回実装：対象『お互い』（`bothPlayers`・バッチA）】（審査時は○）対象『お互い』：ドロー・回復などを両者に。相手にも利益があるので価格×0.4</t>
         </is>
       </c>
     </row>
@@ -40494,12 +40494,12 @@
       </c>
       <c r="L619" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M619" s="13" t="inlineStr">
         <is>
-          <t>次回：最大エナジー増加。暴走しやすく高額。レジェンド限定でシミュレーション必須</t>
+          <t>【今回実装：効果『最大エナジー増加』（`ramp`・バッチB）】（審査時は○）次回：最大エナジー増加。暴走しやすく高額。レジェンド限定でシミュレーション必須</t>
         </is>
       </c>
     </row>
@@ -41511,12 +41511,12 @@
       </c>
       <c r="L636" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M636" s="13" t="inlineStr">
         <is>
-          <t>効果『複写召喚』：場のモンスター1体のコピー（トークン）を自分の場に出す。トークン前提。約40pt</t>
+          <t>【今回実装：効果『複写召喚』（`cloneToken`・バッチB）】（審査時は○）効果『複写召喚』：場のモンスター1体のコピー（トークン）を自分の場に出す。トークン前提。約40pt</t>
         </is>
       </c>
     </row>
@@ -41572,12 +41572,12 @@
       </c>
       <c r="L637" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M637" s="13" t="inlineStr">
         <is>
-          <t>効果『借用』：相手モンスター1体をNターン自分の場に移し、期限で戻す。既存の奪取の期限付き版</t>
+          <t>【今回実装：効果『借用』（#127 と統合）（`borrow`・バッチB）】（審査時は○）効果『借用』：相手モンスター1体をNターン自分の場に移し、期限で戻す。既存の奪取の期限付き版</t>
         </is>
       </c>
     </row>
@@ -41686,12 +41686,12 @@
       </c>
       <c r="L639" s="12" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M639" s="13" t="inlineStr">
         <is>
-          <t>タイミング『起動』：エナジーNを払って効果（1ターン1回）。モンスター・パワーに。UIと起動行動が要る</t>
+          <t>【今回実装：起動型能力（1ターン1回のエナジー払い＝マナ・シンク）（`activated`・バッチC1）】（審査時は○）タイミング『起動』：エナジーNを払って効果（1ターン1回）。モンスター・パワーに。UIと起動行動が要る</t>
         </is>
       </c>
     </row>

--- a/docs/MTG要素カタログ_審査済み.xlsx
+++ b/docs/MTG要素カタログ_審査済み.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="L3" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M3" s="13" t="inlineStr">
         <is>
-          <t>相手の場に攻撃しない『砦』モンスターを置き、倒すと相手が報酬を得る形なら可。裏面・変身は重い</t>
+          <t>【今回実装：効果『砦を築く』＋タイミング『砦を落としたとき』（`siege`・バッチC）】（審査時は△）相手の場に攻撃しない『砦』モンスターを置き、倒すと相手が報酬を得る形なら可。裏面・変身は重い</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M6" s="13" t="inlineStr">
         <is>
-          <t>割り込み不可。予約型の『罠』（相手が攻撃したら発動）なら既存：反撃の拡張として可</t>
+          <t>【今回実装：タイミング『相手のモンスターが攻撃するたび』＋対象『攻撃してきたモンスター』＋能力『罠』（`trap`・バッチA）】（審査時は△）割り込み不可。予約型の『罠』（相手が攻撃したら発動）なら既存：反撃の拡張として可</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M7" s="13" t="inlineStr">
         <is>
-          <t>種族タグをスキルにも付ける案。No.53の種族タグに統合して検討</t>
+          <t>【今回実装：既存の種族（スキルにも付く）で作れる：ルールページの対応表（`mtgGuide`・バッチD）】（審査時は△）種族タグをスキルにも付ける案。No.53の種族タグに統合して検討</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M9" s="13" t="inlineStr">
         <is>
-          <t>重い。パワーに『ターン開始時』効果を持たせる既存の形で代用可</t>
+          <t>【今回実装：カードの能力『忠誠』（＋1／−K の起動）（`loyalty`・バッチC）】（審査時は△）重い。パワーに『ターン開始時』効果を持たせる既存の形で代用可</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M12" s="13" t="inlineStr">
         <is>
-          <t>対戦ごとのランダムなフィールド効果（オプション）なら可。カード要素ではない</t>
+          <t>【今回実装：対戦オプション「次元」（フィールドがランダムに決まり6ターンごとに変わる）（`field`・バッチD）】（審査時は△）対戦ごとのランダムなフィールド効果（オプション）なら可。カード要素ではない</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>リーダー選択（初期HP・手札補正）は別システム。将来のモード候補</t>
+          <t>【今回実装：対戦オプション「リーダー」（`leader`・バッチD）】（審査時は△）リーダー選択（初期HP・手札補正）は別システム。将来のモード候補</t>
         </is>
       </c>
     </row>
@@ -1951,12 +1951,12 @@
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>両者共通のフィールド枠（場に1枚、上書き）。新ゾーンが要るので後回し</t>
+          <t>【今回実装：効果『フィールド』（両者に効く場の効果を上書き）（`setField`・バッチD）】（審査時は△）両者共通のフィールド枠（場に1枚、上書き）。新ゾーンが要るので後回し</t>
         </is>
       </c>
     </row>
@@ -3052,12 +3052,12 @@
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M37" s="13" t="inlineStr">
         <is>
-          <t>ゲージ付きパワー。#154 蓄積カウンターと同じ仕組みで後で</t>
+          <t>【今回実装：蓄積の選択肢「プラン（1回きり）」（`chargePlan`・バッチA）】（審査時は△）ゲージ付きパワー。#154 蓄積カウンターと同じ仕組みで後で</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="L52" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M52" s="13" t="inlineStr">
         <is>
-          <t>No.2と同じ。相手側の攻略目標は新ゾーンが要る</t>
+          <t>【今回実装：効果『砦を築く』（#2 と統合）（`siege`・バッチC）】（審査時は△）No.2と同じ。相手側の攻略目標は新ゾーンが要る</t>
         </is>
       </c>
     </row>
@@ -4348,12 +4348,12 @@
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M57" s="13" t="inlineStr">
         <is>
-          <t>条件達成でモンスターが強化版に変わる『進化』。変身データが要る</t>
+          <t>【今回実装：カードの能力『進化』（達成の仕組み）（`evolve`・バッチC）】（審査時は△）条件達成でモンスターが強化版に変わる『進化』。変身データが要る</t>
         </is>
       </c>
     </row>
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L58" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M58" s="13" t="inlineStr">
         <is>
-          <t>No.56と統合。何度も表裏は不要</t>
+          <t>【今回実装：カードの能力『進化』（#56 と統合。一方通行）（`evolve`・バッチC）】（審査時は△）No.56と統合。何度も表裏は不要</t>
         </is>
       </c>
     </row>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>小技を使った後に本体を出す待機ゾーンが要る。後回し</t>
+          <t>【今回実装：カードの能力『出来事』（待機ゾーン）（`adventure`・バッチC）】（審査時は△）小技を使った後に本体を出す待機ゾーンが要る。後回し</t>
         </is>
       </c>
     </row>
@@ -4803,12 +4803,12 @@
       </c>
       <c r="L64" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M64" s="13" t="inlineStr">
         <is>
-          <t>段階解放は起動型（No.108）が前提。後回し</t>
+          <t>【今回実装：カードの能力『Lvアップ』（パワー＝クラス）（`levelUp`・バッチC）】（審査時は△）段階解放は起動型（No.108）が前提。後回し</t>
         </is>
       </c>
     </row>
@@ -4868,12 +4868,12 @@
       </c>
       <c r="L65" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M65" s="13" t="inlineStr">
         <is>
-          <t>達成条件付きパワー。#154 蓄積カウンターと同じ仕組みで後で</t>
+          <t>【今回実装：カードの能力『事件』（達成の仕組み）（`quest`・バッチC）】（審査時は△）達成条件付きパワー。#154 蓄積カウンターと同じ仕組みで後で</t>
         </is>
       </c>
     </row>
@@ -6550,12 +6550,12 @@
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M91" s="13" t="inlineStr">
         <is>
-          <t>効果『追加ターン』レジェンド限定・1試合1回・高額(60pt+)。オンラインの待ちに注意</t>
+          <t>【今回実装：効果『追加ターン』（レジェンド・1試合1回）（`extraTurn`・バッチC）】（審査時は△）効果『追加ターン』レジェンド限定・1試合1回・高額(60pt+)。オンラインの待ちに注意</t>
         </is>
       </c>
     </row>
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M99" s="13" t="inlineStr">
         <is>
-          <t>既存：自傷デメリットに近い。『エナジー不足時にHP払い』はコスト処理の拡張が要る</t>
+          <t>【今回実装：カードの能力『血の支払い』（`lifePay`・バッチB）】（審査時は△）既存：自傷デメリットに近い。『エナジー不足時にHP払い』はコスト処理の拡張が要る</t>
         </is>
       </c>
     </row>
@@ -8159,12 +8159,12 @@
       </c>
       <c r="L116" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M116" s="13" t="inlineStr">
         <is>
-          <t>特殊勝利は対策手段込みで重い。後回し</t>
+          <t>【今回実装：カードの能力『特殊勝利』（レジェンドのパワー・進み具合を公開）（`altWin`・バッチC）】（審査時は△）特殊勝利は対策手段込みで重い。後回し</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="L120" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M120" s="13" t="inlineStr">
         <is>
-          <t>ドラフトモードは将来候補。カード要素ではない</t>
+          <t>【今回実装：ドラフト戦（CPU 戦）（`draft`・バッチD）】（審査時は△）ドラフトモードは将来候補。カード要素ではない</t>
         </is>
       </c>
     </row>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="L149" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M149" s="13" t="inlineStr">
         <is>
-          <t>効果『消滅の印』：相手モンスターに付与、破壊時に捨て札でなく除外（蘇生・回収対策）。約5pt</t>
+          <t>【今回実装：効果『消滅の印』（`finality`・バッチA）】（審査時は△）効果『消滅の印』：相手モンスターに付与、破壊時に捨て札でなく除外（蘇生・回収対策）。約5pt</t>
         </is>
       </c>
     </row>
@@ -10345,12 +10345,12 @@
       </c>
       <c r="L150" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M150" s="13" t="inlineStr">
         <is>
-          <t>状態『放射能N』：ターン開始時に山札上N枚を捨て札へ、モンスター以外1枚ごとに小ダメージ。期待値で控えめ</t>
+          <t>【今回実装：効果『放射能』（`rad`・バッチA）】（審査時は△）状態『放射能N』：ターン開始時に山札上N枚を捨て札へ、モンスター以外1枚ごとに小ダメージ。期待値で控えめ</t>
         </is>
       </c>
     </row>
@@ -10540,12 +10540,12 @@
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M153" s="13" t="inlineStr">
         <is>
-          <t>プレイヤーの『経験』値を積み、数を参照する効果。参照効果の設計が要るので後回し</t>
+          <t>【今回実装：効果『経験を得る』＋修飾『経験1につき』（`gainExp`・バッチA）】（審査時は△）プレイヤーの『経験』値を積み、数を参照する効果。参照効果の設計が要るので後回し</t>
         </is>
       </c>
     </row>
@@ -10735,12 +10735,12 @@
       </c>
       <c r="L156" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M156" s="13" t="inlineStr">
         <is>
-          <t>効果『氷結』：相手の次の手札1枚を使えなくする等に変形。既存の凍結と差別化が要る</t>
+          <t>【今回実装：効果『氷結』（`iceLock`・バッチA）】（審査時は△）効果『氷結』：相手の次の手札1枚を使えなくする等に変形。既存の凍結と差別化が要る</t>
         </is>
       </c>
     </row>
@@ -10865,12 +10865,12 @@
       </c>
       <c r="L158" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M158" s="13" t="inlineStr">
         <is>
-          <t>英雄譚＝章ごとに効果が出るパワー。ターン数で効果が変わるパワーとして後で検討</t>
+          <t>【今回実装：効果『章を進める』（`advanceSaga`・バッチA）】（審査時は△）英雄譚＝章ごとに効果が出るパワー。ターン数で効果が変わるパワーとして後で検討</t>
         </is>
       </c>
     </row>
@@ -10995,12 +10995,12 @@
       </c>
       <c r="L160" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M160" s="13" t="inlineStr">
         <is>
-          <t>Lvアップ：エナジーを払って段階強化。起動型能力が前提で重い</t>
+          <t>【今回実装：カードの能力『Lvアップ』（Lv の数え）（`levelUp`・バッチC）】（審査時は△）Lvアップ：エナジーを払って段階強化。起動型能力が前提で重い</t>
         </is>
       </c>
     </row>
@@ -11905,12 +11905,12 @@
       </c>
       <c r="L174" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M174" s="13" t="inlineStr">
         <is>
-          <t>#168の派生『卵』：攻撃力0体力Nのトークン、2ターン後に攻撃力+M。変身なしで簡略化</t>
+          <t>【今回実装：効果『培養』（卵のトークン）（`incubate`・バッチA）】（審査時は△）#168の派生『卵』：攻撃力0体力Nのトークン、2ターン後に攻撃力+M。変身なしで簡略化</t>
         </is>
       </c>
     </row>
@@ -12035,12 +12035,12 @@
       </c>
       <c r="L176" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M176" s="13" t="inlineStr">
         <is>
-          <t>効果『探検』：山札の上がモンスターなら手札へ、違えば自分のモンスター攻撃力+N。6pt</t>
+          <t>【今回実装：既存の効果『探検』で作れる：ルールページの対応表（`mtgGuide`・バッチD）】（審査時は△）効果『探検』：山札の上がモンスターなら手札へ、違えば自分のモンスター攻撃力+N。6pt</t>
         </is>
       </c>
     </row>
@@ -12421,12 +12421,12 @@
       </c>
       <c r="L182" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M182" s="13" t="inlineStr">
         <is>
-          <t>#168のトークンに『破壊されたときエナジー+1』を持たせた版で表現できる</t>
+          <t>【今回実装：トークン生成の選択肢「落とし子」（`tokenSpawn`・バッチA）】（審査時は△）#168のトークンに『破壊されたときエナジー+1』を持たせた版で表現できる</t>
         </is>
       </c>
     </row>
@@ -12746,12 +12746,12 @@
       </c>
       <c r="L187" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M187" s="13" t="inlineStr">
         <is>
-          <t>両者共通の昼夜状態。カード使用数で切替、昼夜の条件を追加。共有状態とUIが要る</t>
+          <t>【今回実装：昼と夜（共通の状態）＋条件『昼なら』『夜なら』（`dayNight`・バッチD）】（審査時は△）両者共通の昼夜状態。カード使用数で切替、昼夜の条件を追加。共有状態とUIが要る</t>
         </is>
       </c>
     </row>
@@ -13071,12 +13071,12 @@
       </c>
       <c r="L192" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M192" s="13" t="inlineStr">
         <is>
-          <t>除去不能のパワー。パワー上限3との兼ね合いがあり、レジェンド限定で検討</t>
+          <t>【今回実装：カードの能力『紋章』（`emblem`・バッチC）】（審査時は△）除去不能のパワー。パワー上限3との兼ね合いがあり、レジェンド限定で検討</t>
         </is>
       </c>
     </row>
@@ -13201,12 +13201,12 @@
       </c>
       <c r="L194" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M194" s="13" t="inlineStr">
         <is>
-          <t>ブロックが無い。『攻撃力+Nだが反撃しない・挑発を失う』状態に変形</t>
+          <t>【今回実装：効果『容疑』（`suspect`・バッチA）】（審査時は△）ブロックが無い。『攻撃力+Nだが反撃しない・挑発を失う』状態に変形</t>
         </is>
       </c>
     </row>
@@ -13721,12 +13721,12 @@
       </c>
       <c r="L202" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M202" s="13" t="inlineStr">
         <is>
-          <t>付け替え装備は重い。既存の攻撃力アップ・守備力アップ＋上記『キーワード付与』で代用</t>
+          <t>【今回実装：既存の効果『装備』で作れる：ルールページの対応表（`mtgGuide`・バッチD）】（審査時は△）付け替え装備は重い。既存の攻撃力アップ・守備力アップ＋上記『キーワード付与』で代用</t>
         </is>
       </c>
     </row>
@@ -14176,12 +14176,12 @@
       </c>
       <c r="L209" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M209" s="13" t="inlineStr">
         <is>
-          <t>完全な破壊不能は強すぎ（既存：不屈が近い）。効果『守護』：次の自分ターン開始まで体力1未満にならない</t>
+          <t>【今回実装：効果『守護』（不壊）（`guard`・バッチA）】（審査時は△）完全な破壊不能は強すぎ（既存：不屈が近い）。効果『守護』：次の自分ターン開始まで体力1未満にならない</t>
         </is>
       </c>
     </row>
@@ -14436,12 +14436,12 @@
       </c>
       <c r="L213" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M213" s="13" t="inlineStr">
         <is>
-          <t>属性が無い。効果『加護』：自分のモンスター1体が次の自分ターン開始までダメージを受けない、に変形</t>
+          <t>【今回実装：効果『守護』（加護）（`guard`・バッチA）】（審査時は△）属性が無い。効果『加護』：自分のモンスター1体が次の自分ターン開始までダメージを受けない、に変形</t>
         </is>
       </c>
     </row>
@@ -14501,12 +14501,12 @@
       </c>
       <c r="L214" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M214" s="13" t="inlineStr">
         <is>
-          <t>ブロック無し。飛行実装済みなので『対空』：挑発持ちなら飛行の攻撃も止める、として小キーワード化</t>
+          <t>【今回実装：キーワード『対空』（`reach`・バッチA）】（審査時は△）ブロック無し。飛行実装済みなので『対空』：挑発持ちなら飛行の攻撃も止める、として小キーワード化</t>
         </is>
       </c>
     </row>
@@ -15086,12 +15086,12 @@
       </c>
       <c r="L223" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M223" s="13" t="inlineStr">
         <is>
-          <t>パワー用デメリット『累加維持費』：ターン開始時の自傷が毎ターン増える（upkeepの拡張）</t>
+          <t>【今回実装：デメリット『累加維持費』（`cumulativeUpkeep`・バッチA）】（審査時は△）パワー用デメリット『累加維持費』：ターン開始時の自傷が毎ターン増える（upkeepの拡張）</t>
         </is>
       </c>
     </row>
@@ -15216,12 +15216,12 @@
       </c>
       <c r="L225" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M225" s="13" t="inlineStr">
         <is>
-          <t>デメリット『隔ターン』：パワー/モンスターが1ターンおきにしか働かない。管理が面倒なので保留</t>
+          <t>【今回実装：デメリット『休眠』（1ターンおき）（`dormant`・バッチA）】（審査時は△）デメリット『隔ターン』：パワー/モンスターが1ターンおきにしか働かない。管理が面倒なので保留</t>
         </is>
       </c>
     </row>
@@ -15476,12 +15476,12 @@
       </c>
       <c r="L229" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M229" s="13" t="inlineStr">
         <is>
-          <t>サイクリング実装後、その派生（捨てて山札から指定種類をサーチ）として。単独では保留</t>
+          <t>【今回実装：テンプレート「種類サイクリング」（既存の魂力＋サーチ）（`mtgGuide`・バッチD）】（審査時は△）サイクリング実装後、その派生（捨てて山札から指定種類をサーチ）として。単独では保留</t>
         </is>
       </c>
     </row>
@@ -15931,12 +15931,12 @@
       </c>
       <c r="L236" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M236" s="13" t="inlineStr">
         <is>
-          <t>タイミング『捨てられたとき』（手札喪失など効果で捨てた時のみ）。捨てる効果が少ないので後回し</t>
+          <t>【今回実装：タイミング『捨てられたとき』（`discarded`・バッチA）】（審査時は△）タイミング『捨てられたとき』（手札喪失など効果で捨てた時のみ）。捨てる効果が少ないので後回し</t>
         </is>
       </c>
     </row>
@@ -16841,12 +16841,12 @@
       </c>
       <c r="L250" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M250" s="13" t="inlineStr">
         <is>
-          <t>生け贄でコスト軽減。コスト『自分のモンスター1体を破壊』の追加コスト型として後で</t>
+          <t>【今回実装：カードの能力『現出』（#322 と統合）（`emerge`・バッチB）】（審査時は△）生け贄でコスト軽減。コスト『自分のモンスター1体を破壊』の追加コスト型として後で</t>
         </is>
       </c>
     </row>
@@ -17101,12 +17101,12 @@
       </c>
       <c r="L254" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M254" s="13" t="inlineStr">
         <is>
-          <t>攻撃していない自分のモンスターを攻撃済みにしてコスト−1。ドラッグ操作が複雑化</t>
+          <t>【今回実装：カードの能力『召集』（`convoke`・バッチB）】（審査時は△）攻撃していない自分のモンスターを攻撃済みにしてコスト−1。ドラッグ操作が複雑化</t>
         </is>
       </c>
     </row>
@@ -17166,12 +17166,12 @@
       </c>
       <c r="L255" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M255" s="13" t="inlineStr">
         <is>
-          <t>ドロー置換は重い。山札の上N枚を捨て札に置く部分は『切削』（#421）に統合</t>
+          <t>【今回実装：カードの能力『発掘』（`dredge`・バッチB）】（審査時は△）ドロー置換は重い。山札の上N枚を捨て札に置く部分は『切削』（#421）に統合</t>
         </is>
       </c>
     </row>
@@ -17231,12 +17231,12 @@
       </c>
       <c r="L256" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M256" s="13" t="inlineStr">
         <is>
-          <t>既存：サーチの派生（捨てて同コストを探す）。サイクリング後に</t>
+          <t>【今回実装：サーチの追加指定「このカードと同じコスト」（テンプレート「変成」）（`searchSameCost`・バッチB）】（審査時は△）既存：サーチの派生（捨てて同コストを探す）。サイクリング後に</t>
         </is>
       </c>
     </row>
@@ -17491,12 +17491,12 @@
       </c>
       <c r="L260" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M260" s="13" t="inlineStr">
         <is>
-          <t>ターン開始時に手札から起動は手札が毎ターン入れ替わる本作では機会が少ない</t>
+          <t>【今回実装：カードの能力『予見』＋タイミング『予見』（`forecast`・バッチB）】（審査時は△）ターン開始時に手札から起動は手札が毎ターン入れ替わる本作では機会が少ない</t>
         </is>
       </c>
     </row>
@@ -17816,12 +17816,12 @@
       </c>
       <c r="L265" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M265" s="13" t="inlineStr">
         <is>
-          <t>予約ゾーンが要る。反復（次のターンに発動）で代替</t>
+          <t>【今回実装：カードの能力『待機』（待機ゾーン）（`suspend`・バッチC）】（審査時は△）予約ゾーンが要る。反復（次のターンに発動）で代替</t>
         </is>
       </c>
     </row>
@@ -18076,12 +18076,12 @@
       </c>
       <c r="L269" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M269" s="13" t="inlineStr">
         <is>
-          <t>捨て札を除外してコスト軽減。動的コスト（親和）実装後に</t>
+          <t>【今回実装：カードの能力『探査』（`delve`・バッチB）】（審査時は△）捨て札を除外してコスト軽減。動的コスト（親和）実装後に</t>
         </is>
       </c>
     </row>
@@ -18596,12 +18596,12 @@
       </c>
       <c r="L277" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M277" s="13" t="inlineStr">
         <is>
-          <t>代替コストで召喚時効果だけ使う。二択の使い方UIが要るので保留</t>
+          <t>【今回実装：カードの能力『想起』（`evoke`・バッチB）】（審査時は△）代替コストで召喚時効果だけ使う。二択の使い方UIが要るので保留</t>
         </is>
       </c>
     </row>
@@ -18791,12 +18791,12 @@
       </c>
       <c r="L280" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M280" s="13" t="inlineStr">
         <is>
-          <t>サイクリング実装後の派生（手札から捨ててモンスター1体の攻撃力+N）</t>
+          <t>【今回実装：テンプレート「補強」（既存の魂力＋鍛錬）（`mtgGuide`・バッチD）】（審査時は△）サイクリング実装後の派生（手札から捨ててモンスター1体の攻撃力+N）</t>
         </is>
       </c>
     </row>
@@ -18986,12 +18986,12 @@
       </c>
       <c r="L283" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M283" s="13" t="inlineStr">
         <is>
-          <t>修飾『萎縮』：モンスターへのダメージぶん最大体力も減る（修理で戻らない）。差が小さい</t>
+          <t>【今回実装：修飾『萎縮』（`witherDmg`・バッチA）】（審査時は△）修飾『萎縮』：モンスターへのダメージぶん最大体力も減る（修理で戻らない）。差が小さい</t>
         </is>
       </c>
     </row>
@@ -19051,12 +19051,12 @@
       </c>
       <c r="L284" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M284" s="13" t="inlineStr">
         <is>
-          <t>フラッシュバックの派生（手札1枚を捨てて捨て札から使う）</t>
+          <t>【今回実装：カードの能力『回顧』（`retrace`・バッチB）】（審査時は△）フラッシュバックの派生（手札1枚を捨てて捨て札から使う）</t>
         </is>
       </c>
     </row>
@@ -19116,12 +19116,12 @@
       </c>
       <c r="L285" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M285" s="13" t="inlineStr">
         <is>
-          <t>自分のモンスターを任意数破壊する選択UIが要る</t>
+          <t>【今回実装：カードの能力『貪食』（`devour`・バッチB）】（審査時は△）自分のモンスターを任意数破壊する選択UIが要る</t>
         </is>
       </c>
     </row>
@@ -19246,12 +19246,12 @@
       </c>
       <c r="L287" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M287" s="13" t="inlineStr">
         <is>
-          <t>既存：蘇生の派生（このカード自身を1ターンだけ戻す）</t>
+          <t>【今回実装：カードの能力『一時蘇生』（`unearth`・バッチB）】（審査時は△）既存：蘇生の派生（このカード自身を1ターンだけ戻す）</t>
         </is>
       </c>
     </row>
@@ -19441,12 +19441,12 @@
       </c>
       <c r="L290" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M290" s="13" t="inlineStr">
         <is>
-          <t>エナジーを注いで成長。起動型の操作が要るので保留</t>
+          <t>【今回実装：カードの能力『Lvアップ』（`levelUp`・バッチC）】（審査時は△）エナジーを注いで成長。起動型の操作が要るので保留</t>
         </is>
       </c>
     </row>
@@ -20026,12 +20026,12 @@
       </c>
       <c r="L299" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M299" s="13" t="inlineStr">
         <is>
-          <t>対象を全体に切り替える二択。モード選択UIが要るので保留</t>
+          <t>【今回実装：カードの能力『超過』（`overload`・バッチB）】（審査時は△）対象を全体に切り替える二択。モード選択UIが要るので保留</t>
         </is>
       </c>
     </row>
@@ -20156,12 +20156,12 @@
       </c>
       <c r="L301" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M301" s="13" t="inlineStr">
         <is>
-          <t>二択召喚。デメリット『防衛』と攻撃力アップで近いものが作れる</t>
+          <t>【今回実装：カードの能力『解鎖』（`unleash`・バッチB）】（審査時は△）二択召喚。デメリット『防衛』と攻撃力アップで近いものが作れる</t>
         </is>
       </c>
     </row>
@@ -20416,12 +20416,12 @@
       </c>
       <c r="L305" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M305" s="13" t="inlineStr">
         <is>
-          <t>1枚に効果2組を持ち使用時にどちらか／両方（コスト合計）を選ぶ。選択UIとCPU選択が要る。合計pt+10%</t>
+          <t>【今回実装：テンプレート「融合」（既存のモード選択＋双呪）（`mtgGuide`・バッチD）】（審査時は△）1枚に効果2組を持ち使用時にどちらか／両方（コスト合計）を選ぶ。選択UIとCPU選択が要る。合計pt+10%</t>
         </is>
       </c>
     </row>
@@ -20806,12 +20806,12 @@
       </c>
       <c r="L311" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M311" s="13" t="inlineStr">
         <is>
-          <t>起動型能力が無い。アレンジ：キーワード『鍛錬』攻撃しなかったターン終了時に攻撃力+N。+3pt/N</t>
+          <t>【今回実装：条件『このモンスターがこのターン攻撃していない』（ターン終了時＋鍛錬で長久）（`rested`・バッチA）】（審査時は△）起動型能力が無い。アレンジ：キーワード『鍛錬』攻撃しなかったターン終了時に攻撃力+N。+3pt/N</t>
         </is>
       </c>
     </row>
@@ -21521,12 +21521,12 @@
       </c>
       <c r="L322" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M322" s="13" t="inlineStr">
         <is>
-          <t>ブロック前提。アレンジ：自分より攻撃力が高いモンスターしかいなければ挑発を無視して攻撃できる</t>
+          <t>【今回実装：キーワード『潜伏』（`skulk`・バッチA）】（審査時は△）ブロック前提。アレンジ：自分より攻撃力が高いモンスターしかいなければ挑発を無視して攻撃できる</t>
         </is>
       </c>
     </row>
@@ -21586,12 +21586,12 @@
       </c>
       <c r="L323" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M323" s="13" t="inlineStr">
         <is>
-          <t>生け贄＋コスト軽減。生け贄の仕組みができたら「破壊したモンスターのコスト分軽減」で</t>
+          <t>【今回実装：カードの能力『現出』（`emerge`・バッチB）】（審査時は△）生け贄＋コスト軽減。生け贄の仕組みができたら「破壊したモンスターのコスト分軽減」で</t>
         </is>
       </c>
     </row>
@@ -21651,12 +21651,12 @@
       </c>
       <c r="L324" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M324" s="13" t="inlineStr">
         <is>
-          <t>モード選択＋追加エナジー支払いのUIが要る。放題・段階とまとめて『追加払い』として検討</t>
+          <t>【今回実装：カードの能力『放題』（増呪を統合）（`spree`・バッチB）】（審査時は△）モード選択＋追加エナジー支払いのUIが要る。放題・段階とまとめて『追加払い』として検討</t>
         </is>
       </c>
     </row>
@@ -21976,12 +21976,12 @@
       </c>
       <c r="L329" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M329" s="13" t="inlineStr">
         <is>
-          <t>サーチの対象に「指定したカード名」を足す形ならペアカードを作れる</t>
+          <t>【今回実装：既存のサーチ・抽出「同じ種族」で作れる：ルールページの対応表（`mtgGuide`・バッチD）】（審査時は△）サーチの対象に「指定したカード名」を足す形ならペアカードを作れる</t>
         </is>
       </c>
     </row>
@@ -22496,12 +22496,12 @@
       </c>
       <c r="L337" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M337" s="13" t="inlineStr">
         <is>
-          <t>破壊時に体力1のコピーを場に戻す、など『不屈』寄りのキーワードに。トークン実装後</t>
+          <t>【今回実装：カードの能力『不朽』（`embalm`・バッチB）】（審査時は△）破壊時に体力1のコピーを場に戻す、など『不屈』寄りのキーワードに。トークン実装後</t>
         </is>
       </c>
     </row>
@@ -22561,12 +22561,12 @@
       </c>
       <c r="L338" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M338" s="13" t="inlineStr">
         <is>
-          <t>不朽と同じ。数値固定のコピー（20/20相当）を出す。トークン実装後</t>
+          <t>【今回実装：カードの能力『不朽』の選択肢「永遠」（`embalm`・バッチB）】（審査時は△）不朽と同じ。数値固定のコピー（20/20相当）を出す。トークン実装後</t>
         </is>
       </c>
     </row>
@@ -23471,12 +23471,12 @@
       </c>
       <c r="L352" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M352" s="13" t="inlineStr">
         <is>
-          <t>保留ゾーンが要る。保持（retain）で近い動きはできる</t>
+          <t>【今回実装：カードの能力『予顕』（待機ゾーン・裏向き）（`foretell`・バッチC）】（審査時は△）保留ゾーンが要る。保持（retain）で近い動きはできる</t>
         </is>
       </c>
     </row>
@@ -23601,12 +23601,12 @@
       </c>
       <c r="L354" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M354" s="13" t="inlineStr">
         <is>
-          <t>全体状態（昼夜）は面白いが重い。条件『このターン2枚以上使った』程度に縮めれば既存nthCard</t>
+          <t>【今回実装：昼と夜＋条件『昼なら』『夜なら』（#186 と統合）（`dayNight`・バッチD）】（審査時は△）全体状態（昼夜）は面白いが重い。条件『このターン2枚以上使った』程度に縮めれば既存nthCard</t>
         </is>
       </c>
     </row>
@@ -23666,12 +23666,12 @@
       </c>
       <c r="L355" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M355" s="13" t="inlineStr">
         <is>
-          <t>両面カード要。捨て札から別効果で使う『余韻』（335）に統合</t>
+          <t>【今回実装：既存のフラッシュバック＋「捨て札から使ったとき」で作れる：ルールページの対応表（`mtgGuide`・バッチD）】（審査時は△）両面カード要。捨て札から別効果で使う『余韻』（335）に統合</t>
         </is>
       </c>
     </row>
@@ -23796,12 +23796,12 @@
       </c>
       <c r="L357" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M357" s="13" t="inlineStr">
         <is>
-          <t>追加エナジーで条件を外す。『追加払い』の仕組みの一部として検討</t>
+          <t>【今回実装：カードの能力『切除』（`cleave`・バッチB）】（審査時は△）追加エナジーで条件を外す。『追加払い』の仕組みの一部として検討</t>
         </is>
       </c>
     </row>
@@ -24121,12 +24121,12 @@
       </c>
       <c r="L362" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M362" s="13" t="inlineStr">
         <is>
-          <t>生け贄で効果を2回。生け贄の仕組み（313）ができたら修飾『生け贄で2回』</t>
+          <t>【今回実装：カードの能力『犠牲』（`casualty`・バッチB）】（審査時は△）生け贄で効果を2回。生け贄の仕組み（313）ができたら修飾『生け贄で2回』</t>
         </is>
       </c>
     </row>
@@ -24186,12 +24186,12 @@
       </c>
       <c r="L363" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M363" s="13" t="inlineStr">
         <is>
-          <t>タップ振り替え不可。アレンジ：攻撃時、味方1体の攻撃力ぶんこのターン加算しその味方は攻撃済みに</t>
+          <t>【今回実装：キーワード『後援』（`enlist`・バッチB）】（審査時は△）タップ振り替え不可。アレンジ：攻撃時、味方1体の攻撃力ぶんこのターン加算しその味方は攻撃済みに</t>
         </is>
       </c>
     </row>
@@ -24381,12 +24381,12 @@
       </c>
       <c r="L366" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M366" s="13" t="inlineStr">
         <is>
-          <t>追加払い＋トークン。トークン実装後</t>
+          <t>【今回実装：カードの能力『分隊』（`squad`・バッチB）】（審査時は△）追加払い＋トークン。トークン実装後</t>
         </is>
       </c>
     </row>
@@ -24576,12 +24576,12 @@
       </c>
       <c r="L369" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M369" s="13" t="inlineStr">
         <is>
-          <t>弱版／強版の2つの数値を持つカード。選択UI要、エディター負担大</t>
+          <t>【今回実装：カードの能力『試作』（`prototype`・バッチB）】（審査時は△）弱版／強版の2つの数値を持つカード。選択UI要、エディター負担大</t>
         </is>
       </c>
     </row>
@@ -24901,12 +24901,12 @@
       </c>
       <c r="L374" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M374" s="13" t="inlineStr">
         <is>
-          <t>能力の一時付与が重い。攻撃力アップ＋このターン速攻付与程度ならアレンジ可</t>
+          <t>【今回実装：効果『賛助』（`backup`・バッチA）】（審査時は△）能力の一時付与が重い。攻撃力アップ＋このターン速攻付与程度ならアレンジ可</t>
         </is>
       </c>
     </row>
@@ -24966,12 +24966,12 @@
       </c>
       <c r="L375" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M375" s="13" t="inlineStr">
         <is>
-          <t>生け贄の対象をトークンに。トークンと生け贄の両方が要る</t>
+          <t>【今回実装：カードの能力『協約』＋条件『協約したなら』（`bargain`・バッチB）】（審査時は△）生け贄の対象をトークンに。トークンと生け贄の両方が要る</t>
         </is>
       </c>
     </row>
@@ -25096,12 +25096,12 @@
       </c>
       <c r="L377" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M377" s="13" t="inlineStr">
         <is>
-          <t>伏せ召喚は隠し情報が要る。オンラインのview層で可能だが後回し</t>
+          <t>【今回実装：カードの能力『変装』（裏向きのモンスター）（`disguise`・バッチC）】（審査時は△）伏せ召喚は隠し情報が要る。オンラインのview層で可能だが後回し</t>
         </is>
       </c>
     </row>
@@ -25161,12 +25161,12 @@
       </c>
       <c r="L378" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M378" s="13" t="inlineStr">
         <is>
-          <t>クエスト状態は面白いがUIと進捗管理が重い</t>
+          <t>【今回実装：カードの能力『事件』（#64 と統合）（`quest`・バッチC）】（審査時は△）クエスト状態は面白いがUIと進捗管理が重い</t>
         </is>
       </c>
     </row>
@@ -25226,12 +25226,12 @@
       </c>
       <c r="L379" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M379" s="13" t="inlineStr">
         <is>
-          <t>保留ゾーン要。『貯金』で近い</t>
+          <t>【今回実装：カードの能力『計画』（待機ゾーン）（`plot`・バッチC）】（審査時は△）保留ゾーン要。『貯金』で近い</t>
         </is>
       </c>
     </row>
@@ -25356,12 +25356,12 @@
       </c>
       <c r="L381" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M381" s="13" t="inlineStr">
         <is>
-          <t>追加払いで効果を盛る。ポイント制と重複。『追加払い』として検討</t>
+          <t>【今回実装：カードの能力『放題』（`spree`・バッチB）】（審査時は△）追加払いで効果を盛る。ポイント制と重複。『追加払い』として検討</t>
         </is>
       </c>
     </row>
@@ -25616,12 +25616,12 @@
       </c>
       <c r="L385" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M385" s="13" t="inlineStr">
         <is>
-          <t>カウントダウン召喚。パワーの仕組みで「Nターン後に召喚」効果ならアレンジ可</t>
+          <t>【今回実装：カードの能力『待機』（モンスターの待機＝兆候）（`suspend`・バッチC）】（審査時は△）カウントダウン召喚。パワーの仕組みで「Nターン後に召喚」効果ならアレンジ可</t>
         </is>
       </c>
     </row>
@@ -25876,12 +25876,12 @@
       </c>
       <c r="L389" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M389" s="13" t="inlineStr">
         <is>
-          <t>捨て札から使う＋タップ割引。再活の仕組みができたら</t>
+          <t>【今回実装：カードの能力『調和』（`harmonize`・バッチB）】（審査時は△）捨て札から使う＋タップ割引。再活の仕組みができたら</t>
         </is>
       </c>
     </row>
@@ -26071,12 +26071,12 @@
       </c>
       <c r="L392" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M392" s="13" t="inlineStr">
         <is>
-          <t>段階選択。『追加払い』として検討</t>
+          <t>【今回実装：カードの能力『段階』（`tiered`・バッチB）】（審査時は△）段階選択。『追加払い』として検討</t>
         </is>
       </c>
     </row>
@@ -26201,12 +26201,12 @@
       </c>
       <c r="L394" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M394" s="13" t="inlineStr">
         <is>
-          <t>保留ゾーン要</t>
+          <t>【今回実装：カードの能力『ワープ』（待機ゾーン）（`warp`・バッチC）】（審査時は△）保留ゾーン要</t>
         </is>
       </c>
     </row>
@@ -26331,12 +26331,12 @@
       </c>
       <c r="L396" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M396" s="13" t="inlineStr">
         <is>
-          <t>捨て札にしたカードを使う。再活の仕組みで代替</t>
+          <t>【今回実装：カードの能力『大混乱』（`mayhem`・バッチB）】（審査時は△）捨て札にしたカードを使う。再活の仕組みで代替</t>
         </is>
       </c>
     </row>
@@ -26591,12 +26591,12 @@
       </c>
       <c r="L400" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M400" s="13" t="inlineStr">
         <is>
-          <t>コストと攻撃力の桁が違う。アレンジ：コスト3以上のカードを使うたび攻撃力+N</t>
+          <t>【今回実装：既存の「コスト3以上のカードを使うたび」＋攻撃力アップで作れる：ルールページの対応表（`mtgGuide`・バッチD）】（審査時は△）コストと攻撃力の桁が違う。アレンジ：コスト3以上のカードを使うたび攻撃力+N</t>
         </is>
       </c>
     </row>
@@ -27623,12 +27623,12 @@
       </c>
       <c r="L416" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M416" s="13" t="inlineStr">
         <is>
-          <t>3倍はレジェンド限定の『倍化』上位版として統合</t>
+          <t>【今回実装：倍化の選択肢「3倍」（レジェンド）（`doubleTriple`・バッチA）】（審査時は△）3倍はレジェンド限定の『倍化』上位版として統合</t>
         </is>
       </c>
     </row>
@@ -27688,12 +27688,12 @@
       </c>
       <c r="L417" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M417" s="13" t="inlineStr">
         <is>
-          <t>『HPを入れ替える』はレジェンド限定の逆転手。乱用防止が要る</t>
+          <t>【今回実装：効果『HP交換』（レジェンド・1試合1回）（`swapHp`・バッチC）】（審査時は△）『HPを入れ替える』はレジェンド限定の逆転手。乱用防止が要る</t>
         </is>
       </c>
     </row>
@@ -28858,12 +28858,12 @@
       </c>
       <c r="L435" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M435" s="13" t="inlineStr">
         <is>
-          <t>相手の山札上N枚を上下に振り分け。占術UIの流用で後から追加</t>
+          <t>【今回実装：効果『消術』（`fateseal`・バッチA）】（審査時は△）相手の山札上N枚を上下に振り分け。占術UIの流用で後から追加</t>
         </is>
       </c>
     </row>
@@ -29573,12 +29573,12 @@
       </c>
       <c r="L446" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M446" s="13" t="inlineStr">
         <is>
-          <t>山札トップを裏向き2/2で出す。非公開状態が重い</t>
+          <t>【今回実装：効果『予示』（裏向きのモンスター）（`manifest`・バッチC）】（審査時は△）山札トップを裏向き2/2で出す。非公開状態が重い</t>
         </is>
       </c>
     </row>
@@ -30353,12 +30353,12 @@
       </c>
       <c r="L458" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M458" s="13" t="inlineStr">
         <is>
-          <t>『卵』トークン：2ターン後に孵化してモンスターに。遅延とトークンが揃えば</t>
+          <t>【今回実装：効果『培養』（#173 と統合）（`incubate`・バッチA）】（審査時は△）『卵』トークン：2ターン後に孵化してモンスターに。遅延とトークンが揃えば</t>
         </is>
       </c>
     </row>
@@ -30483,12 +30483,12 @@
       </c>
       <c r="L460" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M460" s="13" t="inlineStr">
         <is>
-          <t>相手が2つの不利益から選ぶ。相手側選択UIとCPUの選び方が要る</t>
+          <t>【今回実装：カードの能力『最悪の二択』（相手がモードを選ぶ）（`villain`・バッチB）】（審査時は△）相手が2つの不利益から選ぶ。相手側選択UIとCPUの選び方が要る</t>
         </is>
       </c>
     </row>
@@ -30808,12 +30808,12 @@
       </c>
       <c r="L465" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M465" s="13" t="inlineStr">
         <is>
-          <t>#193と同じ。『反撃しない代わりに攻撃力+N』に変形</t>
+          <t>【今回実装：効果『容疑』（#193 と統合）（`suspect`・バッチA）】（審査時は△）#193と同じ。『反撃しない代わりに攻撃力+N』に変形</t>
         </is>
       </c>
     </row>
@@ -31003,12 +31003,12 @@
       </c>
       <c r="L468" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M468" s="13" t="inlineStr">
         <is>
-          <t>鍛錬かトークン生成を選ぶ。選択式は二択UIが要る</t>
+          <t>【今回実装：既存のテンプレート「製造」（鍛錬かトークン生成を選ぶ）で作れる：ルールページの対応表（`mtgGuide`・バッチD）】（審査時は△）鍛錬かトークン生成を選ぶ。選択式は二択UIが要る</t>
         </is>
       </c>
     </row>
@@ -32161,12 +32161,12 @@
       </c>
       <c r="L486" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M486" s="13" t="inlineStr">
         <is>
-          <t>#487魂力にまとめる（捨てて自分のモンスター攻撃力+Nの2WAY）</t>
+          <t>【今回実装：テンプレート「湧血」（既存の魂力＋一時強化）（`mtgGuide`・バッチD）】（審査時は△）#487魂力にまとめる（捨てて自分のモンスター攻撃力+Nの2WAY）</t>
         </is>
       </c>
     </row>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="L492" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M492" s="13" t="inlineStr">
         <is>
-          <t>条件『このターン3種類以上のカード（アタック/スキル/パワー/モンスター）を使った』0.6</t>
+          <t>【今回実装：条件『このターン3種類以上のカードを使った』（`converge`・バッチA）】（審査時は△）条件『このターン3種類以上のカード（アタック/スキル/パワー/モンスター）を使った』0.6</t>
         </is>
       </c>
     </row>
@@ -32811,12 +32811,12 @@
       </c>
       <c r="L496" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M496" s="13" t="inlineStr">
         <is>
-          <t>#532スレッショルド/#533に統合：『捨て札にモンスター4枚以上』</t>
+          <t>【今回実装：条件『捨て札にモンスターとパワーが合わせて4枚以上』（`descend`・バッチA）】（審査時は△）#532スレッショルド/#533に統合：『捨て札にモンスター4枚以上』</t>
         </is>
       </c>
     </row>
@@ -34696,12 +34696,12 @@
       </c>
       <c r="L525" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M525" s="13" t="inlineStr">
         <is>
-          <t>#487魂力の捨て札版。捨て札から除外して効果。行動追加が要る</t>
+          <t>【今回実装：カードの能力『相続』＋タイミング『相続』（`renew`・バッチB）】（審査時は△）#487魂力の捨て札版。捨て札から除外して効果。行動追加が要る</t>
         </is>
       </c>
     </row>
@@ -34956,12 +34956,12 @@
       </c>
       <c r="L529" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M529" s="13" t="inlineStr">
         <is>
-          <t>追加コストで対象数増加。エナジー可変払いの仕組みが要り重い</t>
+          <t>【今回実装：カードの能力『奮励』（`strive`・バッチB）】（審査時は△）追加コストで対象数増加。エナジー可変払いの仕組みが要り重い</t>
         </is>
       </c>
     </row>
@@ -35346,12 +35346,12 @@
       </c>
       <c r="L535" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M535" s="13" t="inlineStr">
         <is>
-          <t>#508英雄的のターン1回版として同じ仕組みで出せる</t>
+          <t>【今回実装：タイミング『各ターン初めて自分のカードの対象になったとき』（`valiant`・バッチA）】（審査時は△）#508英雄的のターン1回版として同じ仕組みで出せる</t>
         </is>
       </c>
     </row>
@@ -36289,12 +36289,12 @@
       </c>
       <c r="L550" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M550" s="13" t="inlineStr">
         <is>
-          <t>汎用の永久書き換えは重い。『このカードの数値+N（対戦中ずっと）』に絞れば強度(#554)と同じ仕組みで足りる</t>
+          <t>【今回実装：効果『永久強化』（`perpetual`・バッチA）】（審査時は△）汎用の永久書き換えは重い。『このカードの数値+N（対戦中ずっと）』に絞れば強度(#554)と同じ仕組みで足りる</t>
         </is>
       </c>
     </row>
@@ -36960,12 +36960,12 @@
       </c>
       <c r="L561" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M561" s="13" t="inlineStr">
         <is>
-          <t>相手の山札からランダム3枚見て1枚のコピーを自分の手札へ（コストは自分が払う）。相手カード複製が要る</t>
+          <t>【今回実装：効果『強奪』（`heist`・バッチC）】（審査時は△）相手の山札からランダム3枚見て1枚のコピーを自分の手札へ（コストは自分が払う）。相手カード複製が要る</t>
         </is>
       </c>
     </row>
@@ -37204,12 +37204,12 @@
       </c>
       <c r="L565" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M565" s="13" t="inlineStr">
         <is>
-          <t>召喚時に攻撃力がランダム（±）など。乱数の博打はコイン投げ条件(#639)でまとめて表現する</t>
+          <t>【今回実装：修飾『ばらつき』（`gamble`・バッチA）】（審査時は△）召喚時に攻撃力がランダム（±）など。乱数の博打はコイン投げ条件(#639)でまとめて表現する</t>
         </is>
       </c>
     </row>
@@ -39685,12 +39685,12 @@
       </c>
       <c r="L606" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M606" s="13" t="inlineStr">
         <is>
-          <t>効果『特殊勝利』：例『呪いカードを10枚使ったら勝ち』。進捗表示とCPU対応が要る。レジェンド限定</t>
+          <t>【今回実装：カードの能力『特殊勝利』（#115 と統合）（`altWin`・バッチC）】（審査時は△）効果『特殊勝利』：例『呪いカードを10枚使ったら勝ち』。進捗表示とCPU対応が要る。レジェンド限定</t>
         </is>
       </c>
     </row>
@@ -39811,12 +39811,12 @@
       </c>
       <c r="L608" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M608" s="13" t="inlineStr">
         <is>
-          <t>キーワード『代替コスト』：手札1枚を除外すればコスト0で使える。使用時の選択UIが要る</t>
+          <t>【今回実装：カードの能力『代替コスト』（`pitch`・バッチB）】（審査時は△）キーワード『代替コスト』：手札1枚を除外すればコスト0で使える。使用時の選択UIが要る</t>
         </is>
       </c>
     </row>
@@ -40433,12 +40433,12 @@
       </c>
       <c r="L618" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M618" s="13" t="inlineStr">
         <is>
-          <t>効果『山札削り』：相手の山札の上N枚を除外。山札＋捨て札が0なら敗北に。循環式で効きにくい</t>
+          <t>【今回実装：効果『山札消滅』（`exileMill`・バッチA）】（審査時は△）効果『山札削り』：相手の山札の上N枚を除外。山札＋捨て札が0なら敗北に。循環式で効きにくい</t>
         </is>
       </c>
     </row>
@@ -41145,12 +41145,12 @@
       </c>
       <c r="L630" s="12" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M630" s="13" t="inlineStr">
         <is>
-          <t>ゲーム要素ではなくUI：デッキ画面にコスト分布グラフを出す</t>
+          <t>【今回実装：デッキ構築のコスト分布のグラフ（`manaCurve`・バッチD）】（審査時は△）ゲーム要素ではなくUI：デッキ画面にコスト分布グラフを出す</t>
         </is>
       </c>
     </row>
